--- a/data/trans_bre/Hacinamiento_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,9</t>
+          <t>-2,27; 2,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,59</t>
+          <t>-1,98; 1,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,41</t>
+          <t>-1,95; 2,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,28</t>
+          <t>-1,9; 1,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,0; 40,87</t>
+          <t>-31,68; 42,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-33,92; 37,06</t>
+          <t>-30,76; 45,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,3; 61,78</t>
+          <t>-32,82; 61,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-53,56; 76,95</t>
+          <t>-51,69; 74,09</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,6</t>
+          <t>0,39; 3,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,34</t>
+          <t>0,26; 3,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,11</t>
+          <t>-1,59; 0,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,8</t>
+          <t>-0,81; 1,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,01; 95,01</t>
+          <t>6,89; 99,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 70,6</t>
+          <t>3,78; 78,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,33; 31,75</t>
+          <t>-31,7; 26,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 108,86</t>
+          <t>-29,02; 100,81</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,01</t>
+          <t>-1,26; 3,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,93</t>
+          <t>2,19; 6,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,09</t>
+          <t>-0,87; 4,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,26</t>
+          <t>-1,49; 1,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,26; 180,34</t>
+          <t>-28,01; 151,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>84,47; 1321,29</t>
+          <t>95,26; 1369,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 166,73</t>
+          <t>-19,62; 183,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-63,23; 111,52</t>
+          <t>-59,58; 146,25</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 2,26</t>
+          <t>-0,08; 2,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,51</t>
+          <t>0,39; 2,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,26</t>
+          <t>-0,68; 1,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,16</t>
+          <t>-0,67; 1,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 52,72</t>
+          <t>-1,31; 51,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 59,2</t>
+          <t>7,71; 63,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 32,23</t>
+          <t>-14,21; 32,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 64,46</t>
+          <t>-23,99; 66,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,71</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-10,91%</t>
+          <t>-21,5%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,13</t>
+          <t>-2,26; 1,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,91</t>
+          <t>-1,97; 1,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,33</t>
+          <t>-1,99; 2,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,26</t>
+          <t>-2,64; 0,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,68; 42,54</t>
+          <t>-30,72; 39,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-30,76; 45,27</t>
+          <t>-31,02; 41,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 61,99</t>
+          <t>-32,41; 63,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-51,69; 74,09</t>
+          <t>-56,86; 33,68</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,63</t>
+          <t>0,34; 3,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,53</t>
+          <t>0,25; 3,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,98</t>
+          <t>-1,47; 1,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,78</t>
+          <t>-0,15; 2,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,89; 99,77</t>
+          <t>5,32; 89,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 78,13</t>
+          <t>3,69; 73,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 26,29</t>
+          <t>-30,14; 32,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,02; 100,81</t>
+          <t>-4,72; 98,61</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>0,35</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-2,04%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 3,91</t>
+          <t>-1,36; 3,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,83</t>
+          <t>2,1; 7,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 4,32</t>
+          <t>-0,84; 4,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,64</t>
+          <t>-1,37; 2,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,01; 151,31</t>
+          <t>-29,32; 148,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>95,26; 1369,97</t>
+          <t>91,31; 1755,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 183,18</t>
+          <t>-20,12; 181,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-59,58; 146,25</t>
+          <t>-45,29; 163,73</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,21</t>
+          <t>0,06; 2,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,62</t>
+          <t>0,38; 2,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,28</t>
+          <t>-0,87; 1,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,18</t>
+          <t>-0,31; 1,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 51,23</t>
+          <t>1,01; 52,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,71; 63,38</t>
+          <t>8,52; 63,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 32,21</t>
+          <t>-17,79; 33,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,99; 66,34</t>
+          <t>-9,82; 59,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/Hacinamiento_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/Hacinamiento_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
